--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>221000</v>
+        <v>219500</v>
       </c>
       <c r="C419" t="n">
-        <v>91183</v>
+        <v>188025</v>
       </c>
       <c r="D419" t="n">
-        <v>221568</v>
+        <v>221538</v>
       </c>
       <c r="E419" t="n">
-        <v>230800</v>
+        <v>230506</v>
       </c>
       <c r="F419" t="n">
-        <v>218685</v>
+        <v>218594</v>
       </c>
       <c r="G419" t="n">
-        <v>223684</v>
+        <v>223546</v>
       </c>
       <c r="H419" t="n">
-        <v>0.3592275486579934</v>
+        <v>0.3583889844257961</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>0.3583889844257961</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>224500</v>
+      </c>
+      <c r="C420" t="n">
+        <v>114172</v>
+      </c>
+      <c r="D420" t="n">
+        <v>222980</v>
+      </c>
+      <c r="E420" t="n">
+        <v>230584</v>
+      </c>
+      <c r="F420" t="n">
+        <v>219720</v>
+      </c>
+      <c r="G420" t="n">
+        <v>224428</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0.3637485036489698</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>226500</v>
+        <v>226000</v>
       </c>
       <c r="C421" t="n">
-        <v>15622</v>
+        <v>107122</v>
       </c>
       <c r="D421" t="n">
-        <v>223570</v>
+        <v>223590</v>
       </c>
       <c r="E421" t="n">
-        <v>230567</v>
+        <v>230457</v>
       </c>
       <c r="F421" t="n">
-        <v>219763</v>
+        <v>220685</v>
       </c>
       <c r="G421" t="n">
-        <v>224633</v>
+        <v>224910</v>
       </c>
       <c r="H421" t="n">
-        <v>0.3649941968924511</v>
+        <v>0.3666774019092527</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>0.3666774019092527</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>220500</v>
+      </c>
+      <c r="C422" t="n">
+        <v>90884</v>
+      </c>
+      <c r="D422" t="n">
+        <v>223778</v>
+      </c>
+      <c r="E422" t="n">
+        <v>230228</v>
+      </c>
+      <c r="F422" t="n">
+        <v>221237</v>
+      </c>
+      <c r="G422" t="n">
+        <v>225081</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0.3677164923708884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>0.3677164923708884</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>219000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>89140</v>
+      </c>
+      <c r="D423" t="n">
+        <v>225227</v>
+      </c>
+      <c r="E423" t="n">
+        <v>229004</v>
+      </c>
+      <c r="F423" t="n">
+        <v>221729</v>
+      </c>
+      <c r="G423" t="n">
+        <v>225320</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.3691687883962156</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>0.3691687883962156</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>216500</v>
+      </c>
+      <c r="C424" t="n">
+        <v>117136</v>
+      </c>
+      <c r="D424" t="n">
+        <v>226697</v>
+      </c>
+      <c r="E424" t="n">
+        <v>228558</v>
+      </c>
+      <c r="F424" t="n">
+        <v>221356</v>
+      </c>
+      <c r="G424" t="n">
+        <v>225537</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.3704874002685836</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>0.3704874002685836</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>219000</v>
+      </c>
+      <c r="C425" t="n">
+        <v>121827</v>
+      </c>
+      <c r="D425" t="n">
+        <v>229029</v>
+      </c>
+      <c r="E425" t="n">
+        <v>226366</v>
+      </c>
+      <c r="F425" t="n">
+        <v>220128</v>
+      </c>
+      <c r="G425" t="n">
+        <v>225174</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.3682816117447605</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>0.3682816117447605</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>223000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>100947</v>
+      </c>
+      <c r="D426" t="n">
+        <v>228956</v>
+      </c>
+      <c r="E426" t="n">
+        <v>225218</v>
+      </c>
+      <c r="F426" t="n">
+        <v>219476</v>
+      </c>
+      <c r="G426" t="n">
+        <v>224550</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.3644898430426513</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>219500</v>
+      </c>
+      <c r="C427" t="n">
+        <v>106757</v>
+      </c>
+      <c r="D427" t="n">
+        <v>228838</v>
+      </c>
+      <c r="E427" t="n">
+        <v>224625</v>
+      </c>
+      <c r="F427" t="n">
+        <v>219307</v>
+      </c>
+      <c r="G427" t="n">
+        <v>224257</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.3627094131873341</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>0.3627094131873341</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>219500</v>
+      </c>
+      <c r="C428" t="n">
+        <v>94811</v>
+      </c>
+      <c r="D428" t="n">
+        <v>229865</v>
+      </c>
+      <c r="E428" t="n">
+        <v>223198</v>
+      </c>
+      <c r="F428" t="n">
+        <v>219391</v>
+      </c>
+      <c r="G428" t="n">
+        <v>224151</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.362065298632168</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>0.362065298632168</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>207000</v>
+      </c>
+      <c r="C429" t="n">
+        <v>176417</v>
+      </c>
+      <c r="D429" t="n">
+        <v>229713</v>
+      </c>
+      <c r="E429" t="n">
+        <v>220999</v>
+      </c>
+      <c r="F429" t="n">
+        <v>216316</v>
+      </c>
+      <c r="G429" t="n">
+        <v>222343</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.351078891879903</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>0.351078891879903</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>195300</v>
+      </c>
+      <c r="C430" t="n">
+        <v>257895</v>
+      </c>
+      <c r="D430" t="n">
+        <v>228502</v>
+      </c>
+      <c r="E430" t="n">
+        <v>218003</v>
+      </c>
+      <c r="F430" t="n">
+        <v>208516</v>
+      </c>
+      <c r="G430" t="n">
+        <v>218341</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.3267605291461837</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>0.3267605291461837</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>195400</v>
+      </c>
+      <c r="C431" t="n">
+        <v>188448</v>
+      </c>
+      <c r="D431" t="n">
+        <v>226999</v>
+      </c>
+      <c r="E431" t="n">
+        <v>213902</v>
+      </c>
+      <c r="F431" t="n">
+        <v>203744</v>
+      </c>
+      <c r="G431" t="n">
+        <v>214882</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.3057417343695881</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>0.3057417343695881</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>197000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>188040</v>
+      </c>
+      <c r="D432" t="n">
+        <v>225587</v>
+      </c>
+      <c r="E432" t="n">
+        <v>212570</v>
+      </c>
+      <c r="F432" t="n">
+        <v>200487</v>
+      </c>
+      <c r="G432" t="n">
+        <v>212881</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.2935825530027283</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>0.2935825530027283</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>202500</v>
+      </c>
+      <c r="C433" t="n">
+        <v>132907</v>
+      </c>
+      <c r="D433" t="n">
+        <v>224300</v>
+      </c>
+      <c r="E433" t="n">
+        <v>211669</v>
+      </c>
+      <c r="F433" t="n">
+        <v>198860</v>
+      </c>
+      <c r="G433" t="n">
+        <v>211610</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.2858592548931438</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>0.2858592548931438</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>194300</v>
+      </c>
+      <c r="C434" t="n">
+        <v>147278</v>
+      </c>
+      <c r="D434" t="n">
+        <v>223623</v>
+      </c>
+      <c r="E434" t="n">
+        <v>210225</v>
+      </c>
+      <c r="F434" t="n">
+        <v>196555</v>
+      </c>
+      <c r="G434" t="n">
+        <v>210134</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.2768902635400778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>0.2768902635400778</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>199900</v>
+      </c>
+      <c r="C435" t="n">
+        <v>122313</v>
+      </c>
+      <c r="D435" t="n">
+        <v>223187</v>
+      </c>
+      <c r="E435" t="n">
+        <v>209383</v>
+      </c>
+      <c r="F435" t="n">
+        <v>197496</v>
+      </c>
+      <c r="G435" t="n">
+        <v>210022</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.2762096896704687</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>0.2762096896704687</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>203500</v>
+      </c>
+      <c r="C436" t="n">
+        <v>79292</v>
+      </c>
+      <c r="D436" t="n">
+        <v>222590</v>
+      </c>
+      <c r="E436" t="n">
+        <v>208047</v>
+      </c>
+      <c r="F436" t="n">
+        <v>198797</v>
+      </c>
+      <c r="G436" t="n">
+        <v>209811</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.2749275371125439</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>0.2749275371125439</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>198800</v>
+      </c>
+      <c r="C437" t="n">
+        <v>114618</v>
+      </c>
+      <c r="D437" t="n">
+        <v>221875</v>
+      </c>
+      <c r="E437" t="n">
+        <v>207596</v>
+      </c>
+      <c r="F437" t="n">
+        <v>199364</v>
+      </c>
+      <c r="G437" t="n">
+        <v>209612</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.2737183031835058</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>0.2737183031835058</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>201500</v>
+      </c>
+      <c r="C438" t="n">
+        <v>110760</v>
+      </c>
+      <c r="D438" t="n">
+        <v>221303</v>
+      </c>
+      <c r="E438" t="n">
+        <v>206486</v>
+      </c>
+      <c r="F438" t="n">
+        <v>199050</v>
+      </c>
+      <c r="G438" t="n">
+        <v>208946</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.2696713192802931</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>0.2696713192802931</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>207000</v>
+      </c>
+      <c r="C439" t="n">
+        <v>407318</v>
+      </c>
+      <c r="D439" t="n">
+        <v>220407</v>
+      </c>
+      <c r="E439" t="n">
+        <v>205775</v>
+      </c>
+      <c r="F439" t="n">
+        <v>203770</v>
+      </c>
+      <c r="G439" t="n">
+        <v>209984</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.275978780678994</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>0.275978780678994</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>213500</v>
+      </c>
+      <c r="C440" t="n">
+        <v>360136</v>
+      </c>
+      <c r="D440" t="n">
+        <v>220044</v>
+      </c>
+      <c r="E440" t="n">
+        <v>206271</v>
+      </c>
+      <c r="F440" t="n">
+        <v>207480</v>
+      </c>
+      <c r="G440" t="n">
+        <v>211265</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.2837628443126508</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>0.2837628443126508</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>213000</v>
+      </c>
+      <c r="C441" t="n">
+        <v>423138</v>
+      </c>
+      <c r="D441" t="n">
+        <v>219110</v>
+      </c>
+      <c r="E441" t="n">
+        <v>207123</v>
+      </c>
+      <c r="F441" t="n">
+        <v>209352</v>
+      </c>
+      <c r="G441" t="n">
+        <v>211862</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.2873905460997648</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>0.2873905460997648</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>215000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>186091</v>
+      </c>
+      <c r="D442" t="n">
+        <v>218690</v>
+      </c>
+      <c r="E442" t="n">
+        <v>207539</v>
+      </c>
+      <c r="F442" t="n">
+        <v>210872</v>
+      </c>
+      <c r="G442" t="n">
+        <v>212367</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.290459205065414</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>0.290459205065414</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>222500</v>
+      </c>
+      <c r="C443" t="n">
+        <v>180613</v>
+      </c>
+      <c r="D443" t="n">
+        <v>217808</v>
+      </c>
+      <c r="E443" t="n">
+        <v>208004</v>
+      </c>
+      <c r="F443" t="n">
+        <v>212887</v>
+      </c>
+      <c r="G443" t="n">
+        <v>212900</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.2936980074984656</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>0.2936980074984656</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>206500</v>
+      </c>
+      <c r="C444" t="n">
+        <v>343472</v>
+      </c>
+      <c r="D444" t="n">
+        <v>217263</v>
+      </c>
+      <c r="E444" t="n">
+        <v>207610</v>
+      </c>
+      <c r="F444" t="n">
+        <v>213024</v>
+      </c>
+      <c r="G444" t="n">
+        <v>212632</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.2920694914533291</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성에스디에스_일별_기준주가.xlsx
+++ b/data/삼성에스디에스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>0.2920694914533291</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>203000</v>
+      </c>
+      <c r="C445" t="n">
+        <v>144642</v>
+      </c>
+      <c r="D445" t="n">
+        <v>216980</v>
+      </c>
+      <c r="E445" t="n">
+        <v>207079</v>
+      </c>
+      <c r="F445" t="n">
+        <v>211755</v>
+      </c>
+      <c r="G445" t="n">
+        <v>211938</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.287852364082714</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
